--- a/DateBase/orders/International Ever Green_2026-3-19.xlsx
+++ b/DateBase/orders/International Ever Green_2026-3-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -488,9 +488,62 @@
         <v>485_情人草_Limonium/Misty_undefined_1bunch</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>486_水晶草_Limonium_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>477_泰迪向日葵_sunflower Teddy_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>639_向日葵柠檬黄_undefined_undefined_1stem</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/DateBase/orders/International Ever Green_2026-3-19.xlsx
+++ b/DateBase/orders/International Ever Green_2026-3-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -541,9 +541,62 @@
         <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>4_阳光粉洋桔梗_Sunshine Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>5_绿洋桔梗_Light Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>6_粉边洋桔梗_Pink Edges Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/DateBase/orders/International Ever Green_2026-3-19.xlsx
+++ b/DateBase/orders/International Ever Green_2026-3-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -594,9 +594,49 @@
         <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
   </ignoredErrors>
 </worksheet>
 </file>
